--- a/material/formr_template_eigenesThema.xlsx
+++ b/material/formr_template_eigenesThema.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hochschulefresenius1-my.sharepoint.com/personal/caroline_zygar-hoffmann_charlotte-fresenius-uni_de/Documents/Lehre/WAF/WAF_Folien/material/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{D09DD8A9-CE36-4924-9DE5-E2EC1E5F937A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C578F9C-AE2B-4EDC-AC04-C3D3DAA45E79}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="13_ncr:1_{D09DD8A9-CE36-4924-9DE5-E2EC1E5F937A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2730BFF4-8C44-4B2F-8922-B56881DE1178}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="88">
   <si>
     <t>class</t>
   </si>
@@ -192,17 +192,23 @@
     <t>mc_aut</t>
   </si>
   <si>
+    <t>mc_heading mc_aut</t>
+  </si>
+  <si>
+    <t>AntwortSkala_AutonomieSkala</t>
+  </si>
+  <si>
     <t>__Hinweis: Die Teilnahme ist nur möglich, wenn Sie in alle o.g. Punkte einwilligen.__
 __Hinweis: Speichern Sie sich diese Seite ab, damit Sie bei Bedarf später darauf zugreifen können (per Screenshot oder indem Sie sie auf Papier oder in ein PDF drucken).__</t>
   </si>
   <si>
+    <t>intro_AutonomieSkala</t>
+  </si>
+  <si>
     <t>item1_BeispielSkala</t>
   </si>
   <si>
     <t>intro_BeispielSkala</t>
-  </si>
-  <si>
-    <t>Fragetext</t>
   </si>
   <si>
     <t>mc_width80
@@ -230,12 +236,6 @@
     <t>left500</t>
   </si>
   <si>
-    <t>rechterAntwortanker</t>
-  </si>
-  <si>
-    <t>linkerAntwortanker</t>
-  </si>
-  <si>
     <t>!</t>
   </si>
   <si>
@@ -250,9 +250,6 @@
   </si>
   <si>
     <t>Hiermit willige ich freiwillig in die Verarbeitung meiner Studiendaten durch die Umfragesoftware *formr* und die am Projekt beteiligten Personen zum Zweck der Durchführung des Studie "**[Name einfügen]**" ein. Sofern bzw. soweit die erhobenen Daten unter die besondere Kategorie personenbezogener Daten fallen, erstreckt sich meine Einwilligung auch ausdrücklich hierauf.  Über die Folgen eines Widerrufs der datenschutzrechtlichen Einwilligung (Widerruf mit Wirkung für die Zukunft) bin ich aufgeklärt worden. Die schriftliche Aufklärung, Datenschutzinformation und Einwilligungserklärung habe ich zur Kenntnis genommen und erhalten.</t>
-  </si>
-  <si>
-    <t>Ich willige ein, dass eine zum aktuellem Zeitpunkt nur mit unverhältnismäßigen Aufwand zu deanonymisierende Variante meiner Daten in Form eines „scientific use file“ der wissenschaftlichen Gemeinschaft zur Verfügung gestellt wird.</t>
   </si>
   <si>
     <t xml:space="preserve"># Herzlich Willkommen zu der Studie "[Name der Studie]"
@@ -279,8 +276,7 @@
 __5__</t>
   </si>
   <si>
-    <t>### &lt;center&gt;Überschrift zu Befragungsthema &lt;/center&gt;
-&lt;center&gt;Erklärung/Instruktion&lt;/center&gt;</t>
+    <t>Hiermit willige ich freiwillig ein, dass meine Daten zur weiteren Nutzung als "open data" veröffentlicht werden.</t>
   </si>
   <si>
     <t>&lt;font face="Helvetica"&gt;&lt;font size="4"&gt;&lt;center&gt;&lt;b&gt;Bitte lesen Sie sich zunächst die Teilnahme-Erklärung durch:&lt;/b&gt;&lt;/center&gt;&lt;/font&gt;
@@ -303,7 +299,7 @@
 Zunächst werden Ihre Daten auf zugangsbeschränkten Servern des Leibniz-Rechenzentrums (LRZ) gespeichert. 
 Die Daten werden dann auf Rechnern der am Projekt beteiligten Personen (siehe Punkt 7) verarbeitet.
 Das Pseudonym wird zur Erstellung einer Rückmeldung zu den eigenen Antworten verwendet, und anschließend gelöscht.
-Unter Beachtung von Art. 25 Abs. 3 BayDSG wird eine zum aktuellem Zeitpunkt nur mit unverhältnismäßigen Aufwand zu deanonymisierende Variante der Daten (siehe Punkt 9, ohne Pseudonym)  in Form eines „scientific use file“ (https://de.wikipedia.org/wiki/Scientific-Use-File) der wissenschaftlichen Gemeinschaft zur Verfügung gestellt. Das bedeutet, dass ausschließlich Mitarbeiter wissenschaftlicher Einrichtungen die Daten zu wissenschaftlichen Zwecken nutzen können. Art und Umfang potentieller Nachnutzungen können zum jetzigen Zeitpunkt noch nicht abgesehen werden. Damit folgt diese Studie den Empfehlungen der Deutschen Forschungsgemeinschaft (DFG) zur Qualitätssicherung in Bezug auf Nachprüfbarkeit und Reproduzierbarkeit wissenschaftlicher Ergebnisse, sowie der optimalen Datennachnutzung.
+Die Primärdaten werden (ohne Pseudonym) aus wissenschaftlichen Gründen ohne festgesetzten Termin zur Löschung als "open data" in einem internetbasierten Repositorium namens Open Science Framework (osf.io) zugänglich gemacht. Zweck, Art und Umfang potentieller Nachnutzungen können zum jetzigen Zeitpunkt noch nicht abgesehen werden. Damit folgt diese Studie den Empfehlungen der Deutschen Forschungsgemeinschaft (DFG) zur Qualitätssicherung in Bezug auf Nachprüfbarkeit und Reproduzierbarkeit wissenschaftlicher Ergebnisse, sowie der optimalen Datennachnutzung.
 __7. Beteiligte, Datenflüsse und speichernde Stellen__
 Die Verarbeitung der Umfragedaten erfolgt mit Hilfe der Onlineumfragesoftware „formr“ und mit Hilfe der vom LRZ zur Verfügung gestellten Infrastruktur. 
 Die Daten, die im Rahmen dieser Projekte von Studienteilnehmern/innen erhoben werden, werden, wie unter Punkt 6 beschrieben, verarbeitet. Die Datenverarbeitung erfolgt ausschließlich durch einen beschränkten Personenkreis der Charlotte-Fresenius-Hochschule München (Projektleitung wie unter Punkt 1 beschrieben und Dr. Caroline Zygar-Hoffmann). 
@@ -332,13 +328,28 @@
 Möchten Sie eines dieser Rechte in Anspruch nehmen, wenden Sie sich bitte an die Projektleiter.</t>
   </si>
   <si>
-    <t>mc_heading mc_asq</t>
-  </si>
-  <si>
-    <t>AntwortSkala_ASQ</t>
-  </si>
-  <si>
-    <t>intro_ASQSkala</t>
+    <t>Fragetext: z.B. Ich bin zufrieden mit meiner Leistung in der Statistik-Prüfung.</t>
+  </si>
+  <si>
+    <t>trifft überhaupt nicht zu</t>
+  </si>
+  <si>
+    <t>trifft voll und ganz zu</t>
+  </si>
+  <si>
+    <t>mc_width60</t>
+  </si>
+  <si>
+    <t>### &lt;center&gt;Überschrift zu Befragungsthema &lt;/center&gt;
+&lt;br&gt;
+&lt;center&gt;Erklärung/Instruktion&lt;/center&gt;
+&lt;br&gt;</t>
+  </si>
+  <si>
+    <t>### &lt;center&gt;Überschrift zu Befragungsthema &lt;/center&gt;
+&lt;br&gt;
+&lt;center&gt;Erklärung/Instruktion, z.B. Bitte füllen Sie die folgenden Fragen auf einer Skala von 1 bis 5 aus, wobei 1 für "trifft überhaupt nicht zu" und 5 für "trifft voll und ganz zu" steht. &lt;/center&gt;
+&lt;br&gt;</t>
   </si>
 </sst>
 </file>
@@ -466,6 +477,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -778,7 +793,7 @@
     <col min="5" max="5" width="23.125" customWidth="1"/>
     <col min="6" max="6" width="13.75" customWidth="1"/>
     <col min="7" max="7" width="91.25" style="5" customWidth="1"/>
-    <col min="8" max="8" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.25" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22.125" bestFit="1" customWidth="1"/>
     <col min="10" max="20" width="10.75" customWidth="1"/>
   </cols>
@@ -859,7 +874,7 @@
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
@@ -912,7 +927,7 @@
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H4"/>
       <c r="I4"/>
@@ -921,7 +936,7 @@
     </row>
     <row r="5" spans="1:20" s="7" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B5" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
@@ -943,7 +958,7 @@
     </row>
     <row r="6" spans="1:20" s="7" customFormat="1" ht="110.25" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
@@ -963,9 +978,9 @@
       <c r="J6"/>
       <c r="K6"/>
     </row>
-    <row r="7" spans="1:20" s="7" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" s="7" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B7" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
@@ -978,7 +993,7 @@
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="5" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
@@ -996,7 +1011,7 @@
       </c>
       <c r="F8"/>
       <c r="G8" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H8"/>
       <c r="J8"/>
@@ -1029,11 +1044,11 @@
       </c>
       <c r="D10"/>
       <c r="E10" s="8" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F10"/>
       <c r="G10" s="9" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H10"/>
       <c r="J10"/>
@@ -1041,20 +1056,23 @@
     </row>
     <row r="11" spans="1:20" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
+      <c r="B11" s="9" t="s">
+        <v>85</v>
+      </c>
       <c r="C11" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -1095,11 +1113,11 @@
       </c>
       <c r="D13"/>
       <c r="E13" s="8" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="F13"/>
       <c r="G13" s="9" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="H13"/>
       <c r="J13"/>
@@ -1107,13 +1125,13 @@
     </row>
     <row r="14" spans="1:20" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="G14" s="9"/>
       <c r="I14" s="7"/>
@@ -1130,7 +1148,7 @@
     </row>
     <row r="15" spans="1:20" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C15" t="s">
         <v>22</v>
@@ -1155,7 +1173,7 @@
     </row>
     <row r="16" spans="1:20" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s">
         <v>22</v>
@@ -1203,10 +1221,10 @@
         <v>19</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
@@ -1222,7 +1240,7 @@
     </row>
     <row r="19" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B19" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
         <v>21</v>
@@ -1231,7 +1249,7 @@
         <v>39</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H19" t="s">
         <v>40</v>
@@ -1253,7 +1271,7 @@
     </row>
     <row r="20" spans="1:20" s="7" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
         <v>20</v>
@@ -1263,7 +1281,7 @@
         <v>38</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>42</v>
@@ -1307,7 +1325,7 @@
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1348,7 +1366,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1357,7 +1375,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1366,7 +1384,7 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -1384,7 +1402,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/material/formr_template_eigenesThema.xlsx
+++ b/material/formr_template_eigenesThema.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hochschulefresenius1-my.sharepoint.com/personal/caroline_zygar-hoffmann_charlotte-fresenius-uni_de/Documents/Lehre/WAF/WAF_Folien/material/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="13_ncr:1_{D09DD8A9-CE36-4924-9DE5-E2EC1E5F937A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2730BFF4-8C44-4B2F-8922-B56881DE1178}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="13_ncr:1_{D09DD8A9-CE36-4924-9DE5-E2EC1E5F937A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{179CC767-05A6-402C-9915-4C3CE08B27BA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -149,10 +149,6 @@
     <t>nein</t>
   </si>
   <si>
-    <t>Für die Zuordnung der Rückmeldungen arbeiten wir mit Pseudonymen. Bitte fügen Sie daher hier einen selbstgewählten, zufälligen 10-stelligen Buchstabencode ein, z.B. generiert mit folgender Website: https://randomwordgenerator.com/password.php
-Mit diesem Pseudonym können Sie im Nachgang Ihre eigene Rückmeldung zu den Daten identifizieren. Sie müssen sich den Buchstabencode also notieren. Halten Sie den Buchstabencode geheim, wenn Sie nicht möchten, dass andere die Rückmeldung Ihnen zuordnen können.</t>
-  </si>
-  <si>
     <t>danke</t>
   </si>
   <si>
@@ -267,9 +263,6 @@
   </si>
   <si>
     <t>__2__</t>
-  </si>
-  <si>
-    <t>__3__</t>
   </si>
   <si>
     <t>__Trifft voll und ganz zu__
@@ -342,13 +335,21 @@
   <si>
     <t>### &lt;center&gt;Überschrift zu Befragungsthema &lt;/center&gt;
 &lt;br&gt;
-&lt;center&gt;Erklärung/Instruktion&lt;/center&gt;
+&lt;center&gt;Erklärung/Instruktion, z.B. Bitte füllen Sie die folgenden Fragen auf einer Skala von 1 bis 5 aus, wobei 1 für "trifft überhaupt nicht zu" und 5 für "trifft voll und ganz zu" steht. &lt;/center&gt;
 &lt;br&gt;</t>
+  </si>
+  <si>
+    <t>Für die Zuordnung der Rückmeldungen arbeiten wir mit Pseudonymen. Bitte fügen Sie daher hier einen selbstgewählten, zufälligen 10-stelligen Buchstabencode ein, z.B. generiert mit folgender Website (den Link in einem neuen Browsertab öffnen, da man sonst die Studie verlässt und nicht mehr zurückkommt): https://randomwordgenerator.com/password.php
+Mit diesem Pseudonym können Sie im Nachgang Ihre eigene Rückmeldung zu den Daten identifizieren. Sie müssen sich den Buchstabencode also notieren. Halten Sie den Buchstabencode geheim, wenn Sie nicht möchten, dass andere die Rückmeldung Ihnen zuordnen können.</t>
+  </si>
+  <si>
+    <t>__Trifft mittel-mäßig zu__
+__3__</t>
   </si>
   <si>
     <t>### &lt;center&gt;Überschrift zu Befragungsthema &lt;/center&gt;
 &lt;br&gt;
-&lt;center&gt;Erklärung/Instruktion, z.B. Bitte füllen Sie die folgenden Fragen auf einer Skala von 1 bis 5 aus, wobei 1 für "trifft überhaupt nicht zu" und 5 für "trifft voll und ganz zu" steht. &lt;/center&gt;
+&lt;center&gt;Erklärung/Instruktion: Dafür muss man in der Publikation vom Messinstrument nachlesen wie die korrekte Instruktion lautet; falls diese Instruktion nicht bereits eine Beschreibung der verbalen Anker enthält, diese bitte hier wiederholen (um Darstellungsfehler bei mobilen Ansichten zu umgehen), z.B. 1 = trifft überhaupt nicht zu, 3 = trifft mittelmäßig zu, 5 = trifft voll und ganz zu. &lt;/center&gt;
 &lt;br&gt;</t>
   </si>
 </sst>
@@ -477,10 +478,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -789,7 +786,7 @@
     <col min="1" max="1" width="19.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.875" customWidth="1"/>
+    <col min="4" max="4" width="11.375" customWidth="1"/>
     <col min="5" max="5" width="23.125" customWidth="1"/>
     <col min="6" max="6" width="13.75" customWidth="1"/>
     <col min="7" max="7" width="91.25" style="5" customWidth="1"/>
@@ -800,7 +797,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -862,7 +859,7 @@
     </row>
     <row r="2" spans="1:20" ht="314.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3" t="s">
@@ -874,7 +871,7 @@
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
@@ -917,7 +914,7 @@
     </row>
     <row r="4" spans="1:20" s="7" customFormat="1" ht="199.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
@@ -927,7 +924,7 @@
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H4"/>
       <c r="I4"/>
@@ -936,20 +933,20 @@
     </row>
     <row r="5" spans="1:20" s="7" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B5" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
         <v>29</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H5"/>
       <c r="I5"/>
@@ -958,20 +955,20 @@
     </row>
     <row r="6" spans="1:20" s="7" customFormat="1" ht="110.25" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
         <v>32</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H6"/>
       <c r="I6"/>
@@ -980,20 +977,20 @@
     </row>
     <row r="7" spans="1:20" s="7" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B7" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E7" t="s">
         <v>33</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
@@ -1011,7 +1008,7 @@
       </c>
       <c r="F8"/>
       <c r="G8" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H8"/>
       <c r="J8"/>
@@ -1036,7 +1033,7 @@
     </row>
     <row r="10" spans="1:20" s="7" customFormat="1" ht="199.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B10"/>
       <c r="C10" t="s">
@@ -1044,11 +1041,11 @@
       </c>
       <c r="D10"/>
       <c r="E10" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F10"/>
       <c r="G10" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H10"/>
       <c r="J10"/>
@@ -1057,22 +1054,22 @@
     <row r="11" spans="1:20" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G11" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I11" s="8" t="s">
         <v>82</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>84</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -1105,7 +1102,7 @@
     </row>
     <row r="13" spans="1:20" s="7" customFormat="1" ht="199.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B13"/>
       <c r="C13" t="s">
@@ -1113,11 +1110,11 @@
       </c>
       <c r="D13"/>
       <c r="E13" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F13"/>
       <c r="G13" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H13"/>
       <c r="J13"/>
@@ -1125,13 +1122,13 @@
     </row>
     <row r="14" spans="1:20" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C14" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>56</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>57</v>
       </c>
       <c r="G14" s="9"/>
       <c r="I14" s="7"/>
@@ -1148,16 +1145,16 @@
     </row>
     <row r="15" spans="1:20" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
         <v>22</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I15" s="7"/>
       <c r="K15" s="3"/>
@@ -1173,16 +1170,16 @@
     </row>
     <row r="16" spans="1:20" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
         <v>22</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I16" s="7"/>
       <c r="K16" s="3"/>
@@ -1203,7 +1200,7 @@
       </c>
       <c r="D17"/>
       <c r="E17" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F17"/>
       <c r="G17" s="5" t="s">
@@ -1215,16 +1212,16 @@
     </row>
     <row r="18" spans="1:20" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>19</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
@@ -1240,7 +1237,7 @@
     </row>
     <row r="19" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B19" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C19" t="s">
         <v>21</v>
@@ -1249,7 +1246,7 @@
         <v>39</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H19" t="s">
         <v>40</v>
@@ -1271,7 +1268,7 @@
     </row>
     <row r="20" spans="1:20" s="7" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
         <v>20</v>
@@ -1281,10 +1278,10 @@
         <v>38</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="H20"/>
       <c r="I20"/>
@@ -1297,10 +1294,10 @@
         <v>19</v>
       </c>
       <c r="E21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
@@ -1325,7 +1322,7 @@
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1360,13 +1357,13 @@
     </row>
     <row r="2" spans="1:3" ht="149.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1375,16 +1372,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
-        <v>78</v>
+      <c r="C4" s="5" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -1393,7 +1390,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="47.25" x14ac:dyDescent="0.25">
@@ -1402,7 +1399,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
